--- a/content/notes/travel/travel.xlsx
+++ b/content/notes/travel/travel.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ravi/programs/jonpine.github.io/content/notes/travel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA10249E-7232-B946-87D6-C7FA1C71D1F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E4774D1-565B-3745-8FCC-ABEA7097D9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="21580" activeTab="4" xr2:uid="{FBDD8960-5B88-4843-A147-F58767FB427D}"/>
   </bookViews>
@@ -46,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2454" uniqueCount="879">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2455" uniqueCount="880">
   <si>
     <t>Check In</t>
   </si>
@@ -2106,9 +2106,6 @@
     <t>Delft</t>
   </si>
   <si>
-    <t>King Kong Hostel</t>
-  </si>
-  <si>
     <t>Kinderdijk</t>
   </si>
   <si>
@@ -2683,6 +2680,12 @@
   </si>
   <si>
     <t>AC - 17.5</t>
+  </si>
+  <si>
+    <t>5 days</t>
+  </si>
+  <si>
+    <t>Hostel Room</t>
   </si>
 </sst>
 </file>
@@ -3067,6 +3070,15 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3077,15 +3089,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -4391,11 +4394,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -4639,13 +4642,13 @@
       <c r="J12" s="90"/>
       <c r="K12" s="90"/>
       <c r="L12" s="90"/>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="83"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="77"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C13" s="96" t="s">
@@ -4669,10 +4672,10 @@
       <c r="P13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="77" t="s">
+      <c r="Q13" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R13" s="78"/>
+      <c r="R13" s="81"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C14" s="12" t="s">
@@ -4692,13 +4695,13 @@
         <v>53</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J14" s="88" t="s">
         <v>7</v>
       </c>
       <c r="K14" s="88"/>
-      <c r="L14" s="78"/>
+      <c r="L14" s="81"/>
       <c r="N14" s="3" t="s">
         <v>572</v>
       </c>
@@ -4969,13 +4972,13 @@
       <c r="J24" s="74"/>
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
-      <c r="N24" s="81" t="s">
+      <c r="N24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O24" s="82"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="56"/>
@@ -5003,7 +5006,7 @@
       <c r="P25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q25" s="77" t="s">
+      <c r="Q25" s="80" t="s">
         <v>7</v>
       </c>
       <c r="R25" s="88"/>
@@ -5147,13 +5150,13 @@
       </c>
       <c r="K31" s="74"/>
       <c r="L31" s="74"/>
-      <c r="N31" s="81" t="s">
+      <c r="N31" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="83"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="77"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="55"/>
@@ -5281,12 +5284,12 @@
       </c>
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
-      <c r="N36" s="81" t="s">
+      <c r="N36" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="83"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="55"/>
@@ -5453,7 +5456,7 @@
         <v>15</v>
       </c>
       <c r="J43" s="152" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K43" s="157"/>
       <c r="L43" s="153"/>
@@ -5480,8 +5483,8 @@
     </row>
     <row r="45" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C45" s="55"/>
-      <c r="D45" s="79"/>
-      <c r="E45" s="80"/>
+      <c r="D45" s="82"/>
+      <c r="E45" s="83"/>
       <c r="F45" s="1"/>
       <c r="G45" s="1"/>
       <c r="H45" s="1"/>
@@ -5504,8 +5507,8 @@
     </row>
     <row r="47" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="80"/>
+      <c r="D47" s="82"/>
+      <c r="E47" s="83"/>
       <c r="F47" s="3"/>
       <c r="G47" s="4"/>
       <c r="H47" s="4"/>
@@ -5516,8 +5519,8 @@
     </row>
     <row r="48" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C48" s="1"/>
-      <c r="D48" s="79"/>
-      <c r="E48" s="80"/>
+      <c r="D48" s="82"/>
+      <c r="E48" s="83"/>
       <c r="F48" s="14"/>
       <c r="G48" s="4">
         <f>SUM(G15:G46)</f>
@@ -5560,18 +5563,18 @@
       <c r="L50" s="90"/>
     </row>
     <row r="51" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C51" s="81" t="s">
+      <c r="C51" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D51" s="82"/>
-      <c r="E51" s="82"/>
-      <c r="F51" s="82"/>
-      <c r="G51" s="82"/>
-      <c r="H51" s="82"/>
-      <c r="I51" s="82"/>
-      <c r="J51" s="82"/>
-      <c r="K51" s="82"/>
-      <c r="L51" s="83"/>
+      <c r="D51" s="76"/>
+      <c r="E51" s="76"/>
+      <c r="F51" s="76"/>
+      <c r="G51" s="76"/>
+      <c r="H51" s="76"/>
+      <c r="I51" s="76"/>
+      <c r="J51" s="76"/>
+      <c r="K51" s="76"/>
+      <c r="L51" s="77"/>
     </row>
     <row r="52" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C52" s="6" t="s">
@@ -5705,9 +5708,9 @@
         <v>0</v>
       </c>
       <c r="I59" s="3"/>
-      <c r="J59" s="75"/>
-      <c r="K59" s="75"/>
-      <c r="L59" s="75"/>
+      <c r="J59" s="78"/>
+      <c r="K59" s="78"/>
+      <c r="L59" s="78"/>
     </row>
     <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D60" s="38"/>
@@ -5746,8 +5749,6 @@
     <mergeCell ref="J43:L43"/>
     <mergeCell ref="D44:E44"/>
     <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="D31:E31"/>
     <mergeCell ref="J31:L31"/>
     <mergeCell ref="N29:R30"/>
     <mergeCell ref="D39:E39"/>
@@ -5763,8 +5764,6 @@
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="J38:L38"/>
     <mergeCell ref="N31:R31"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="J22:L22"/>
     <mergeCell ref="Q27:R27"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="J23:L23"/>
@@ -5787,10 +5786,8 @@
     <mergeCell ref="J35:L35"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="N22:R23"/>
-    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="D31:E31"/>
     <mergeCell ref="J18:L18"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="J19:L19"/>
@@ -5798,6 +5795,8 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="J24:L24"/>
     <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="J22:L22"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="J25:L25"/>
     <mergeCell ref="D26:E26"/>
@@ -5818,6 +5817,10 @@
     <mergeCell ref="J20:L20"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="J21:L21"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="N22:R23"/>
+    <mergeCell ref="D18:E18"/>
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="Q13:R13"/>
     <mergeCell ref="I9:K9"/>
@@ -5876,11 +5879,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -6177,13 +6180,13 @@
       <c r="J12" s="94"/>
       <c r="K12" s="108"/>
       <c r="L12" s="3"/>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="83"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="77"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B13" s="13"/>
@@ -6206,10 +6209,10 @@
       <c r="P13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="77" t="s">
+      <c r="Q13" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R13" s="78"/>
+      <c r="R13" s="81"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B14" s="13"/>
@@ -6224,7 +6227,7 @@
       <c r="K14" s="115"/>
       <c r="L14" s="3"/>
       <c r="N14" s="3" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O14" s="3"/>
       <c r="P14" s="3"/>
@@ -6333,13 +6336,13 @@
         <v>53</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J19" s="88" t="s">
         <v>7</v>
       </c>
       <c r="K19" s="88"/>
-      <c r="L19" s="78"/>
+      <c r="L19" s="81"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
@@ -6372,7 +6375,7 @@
     <row r="21" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C21" s="55"/>
       <c r="D21" s="74" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="E21" s="74"/>
       <c r="F21" s="1" t="s">
@@ -6401,7 +6404,7 @@
     <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="56"/>
       <c r="D22" s="74" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="E22" s="74"/>
       <c r="F22" s="1" t="s">
@@ -6424,7 +6427,7 @@
     <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="56"/>
       <c r="D23" s="74" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="E23" s="74"/>
       <c r="F23" s="1" t="s">
@@ -6447,7 +6450,7 @@
     <row r="24" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C24" s="56"/>
       <c r="D24" s="74" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E24" s="74"/>
       <c r="F24" s="1" t="s">
@@ -6461,18 +6464,18 @@
       <c r="J24" s="74"/>
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
-      <c r="N24" s="81" t="s">
+      <c r="N24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O24" s="82"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="56"/>
       <c r="D25" s="74" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E25" s="74"/>
       <c r="F25" s="1" t="s">
@@ -6495,7 +6498,7 @@
       <c r="P25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q25" s="77" t="s">
+      <c r="Q25" s="80" t="s">
         <v>7</v>
       </c>
       <c r="R25" s="88"/>
@@ -6503,7 +6506,7 @@
     <row r="26" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C26" s="56"/>
       <c r="D26" s="74" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E26" s="74"/>
       <c r="F26" s="1" t="s">
@@ -6528,11 +6531,11 @@
     <row r="27" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C27" s="56"/>
       <c r="D27" s="74" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E27" s="74"/>
       <c r="F27" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G27" s="1">
         <v>12</v>
@@ -6551,11 +6554,11 @@
     <row r="28" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C28" s="56"/>
       <c r="D28" s="74" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E28" s="74"/>
       <c r="F28" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="G28" s="1">
         <v>13</v>
@@ -6577,7 +6580,7 @@
     <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="56"/>
       <c r="D29" s="74" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="E29" s="74"/>
       <c r="F29" s="1" t="s">
@@ -6600,7 +6603,7 @@
     <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="56"/>
       <c r="D30" s="74" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="E30" s="74"/>
       <c r="F30" s="1" t="s">
@@ -6623,7 +6626,7 @@
     <row r="31" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C31" s="56"/>
       <c r="D31" s="74" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="E31" s="74"/>
       <c r="F31" s="1" t="s">
@@ -6637,18 +6640,18 @@
       <c r="J31" s="74"/>
       <c r="K31" s="74"/>
       <c r="L31" s="74"/>
-      <c r="N31" s="81" t="s">
+      <c r="N31" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="83"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="77"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="56"/>
       <c r="D32" s="74" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="E32" s="74"/>
       <c r="F32" s="1" t="s">
@@ -6682,7 +6685,7 @@
     <row r="33" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C33" s="56"/>
       <c r="D33" s="74" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="E33" s="74"/>
       <c r="F33" s="1" t="s">
@@ -6705,7 +6708,7 @@
     <row r="34" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C34" s="56"/>
       <c r="D34" s="74" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="E34" s="74"/>
       <c r="F34" s="1" t="s">
@@ -6723,7 +6726,7 @@
     <row r="35" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C35" s="56"/>
       <c r="D35" s="74" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="E35" s="74"/>
       <c r="F35" s="1" t="s">
@@ -6741,7 +6744,7 @@
     <row r="36" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C36" s="56"/>
       <c r="D36" s="74" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="E36" s="74"/>
       <c r="F36" s="1" t="s">
@@ -6757,17 +6760,17 @@
       </c>
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
-      <c r="N36" s="81" t="s">
+      <c r="N36" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="83"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="55"/>
       <c r="D37" s="74" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="E37" s="74"/>
       <c r="F37" s="1" t="s">
@@ -6799,7 +6802,7 @@
     <row r="38" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C38" s="55"/>
       <c r="D38" s="74" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="E38" s="74"/>
       <c r="F38" s="1" t="s">
@@ -6832,7 +6835,7 @@
     <row r="39" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C39" s="55"/>
       <c r="D39" s="74" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="E39" s="74"/>
       <c r="F39" s="1" t="s">
@@ -6851,7 +6854,7 @@
     <row r="40" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C40" s="55"/>
       <c r="D40" s="74" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="E40" s="74"/>
       <c r="F40" s="1" t="s">
@@ -6871,7 +6874,7 @@
     <row r="41" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C41" s="55"/>
       <c r="D41" s="74" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="E41" s="74"/>
       <c r="F41" s="1" t="s">
@@ -6891,7 +6894,7 @@
     <row r="42" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C42" s="55"/>
       <c r="D42" s="74" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="E42" s="74"/>
       <c r="F42" s="1" t="s">
@@ -6911,7 +6914,7 @@
     <row r="43" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C43" s="55"/>
       <c r="D43" s="74" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="E43" s="74"/>
       <c r="F43" s="1" t="s">
@@ -6931,7 +6934,7 @@
     <row r="44" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C44" s="56"/>
       <c r="D44" s="74" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="E44" s="74"/>
       <c r="F44" s="1" t="s">
@@ -6951,7 +6954,7 @@
     <row r="45" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C45" s="56"/>
       <c r="D45" s="74" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="E45" s="74"/>
       <c r="F45" s="1" t="s">
@@ -6971,7 +6974,7 @@
     <row r="46" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C46" s="56"/>
       <c r="D46" s="74" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="E46" s="74"/>
       <c r="F46" s="1" t="s">
@@ -6989,7 +6992,7 @@
     <row r="47" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C47" s="56"/>
       <c r="D47" s="74" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="E47" s="74"/>
       <c r="F47" s="1" t="s">
@@ -7007,7 +7010,7 @@
     <row r="48" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C48" s="56"/>
       <c r="D48" s="74" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="E48" s="74"/>
       <c r="F48" s="1" t="s">
@@ -7025,11 +7028,11 @@
     <row r="49" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C49" s="55"/>
       <c r="D49" s="74" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="E49" s="74"/>
       <c r="F49" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G49" s="1">
         <v>19.5</v>
@@ -7045,7 +7048,7 @@
     <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="56"/>
       <c r="D50" s="74" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E50" s="74"/>
       <c r="F50" s="1" t="s">
@@ -7065,7 +7068,7 @@
     <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="56"/>
       <c r="D51" s="74" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E51" s="74"/>
       <c r="F51" s="1" t="s">
@@ -7083,7 +7086,7 @@
     <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="56"/>
       <c r="D52" s="74" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E52" s="74"/>
       <c r="F52" s="1" t="s">
@@ -7103,7 +7106,7 @@
     <row r="53" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C53" s="56"/>
       <c r="D53" s="74" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E53" s="74"/>
       <c r="F53" s="1" t="s">
@@ -7121,7 +7124,7 @@
     <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="56"/>
       <c r="D54" s="74" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E54" s="74"/>
       <c r="F54" s="1" t="s">
@@ -7139,7 +7142,7 @@
     <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="56"/>
       <c r="D55" s="74" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E55" s="74"/>
       <c r="F55" s="1" t="s">
@@ -7157,7 +7160,7 @@
     <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="56"/>
       <c r="D56" s="74" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="E56" s="74"/>
       <c r="F56" s="1" t="s">
@@ -7177,7 +7180,7 @@
     <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="56"/>
       <c r="D57" s="74" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E57" s="74"/>
       <c r="F57" s="1" t="s">
@@ -7195,7 +7198,7 @@
     <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="56"/>
       <c r="D58" s="74" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="E58" s="74"/>
       <c r="F58" s="1" t="s">
@@ -7215,7 +7218,7 @@
     <row r="59" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C59" s="56"/>
       <c r="D59" s="74" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="E59" s="74"/>
       <c r="F59" s="1" t="s">
@@ -7235,7 +7238,7 @@
     <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="56"/>
       <c r="D60" s="74" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="E60" s="74"/>
       <c r="F60" s="1" t="s">
@@ -7255,7 +7258,7 @@
     <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="56"/>
       <c r="D61" s="74" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E61" s="74"/>
       <c r="F61" s="1" t="s">
@@ -7275,7 +7278,7 @@
     <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="56"/>
       <c r="D62" s="74" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="E62" s="74"/>
       <c r="F62" s="1" t="s">
@@ -7293,7 +7296,7 @@
     <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="56"/>
       <c r="D63" s="74" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="E63" s="74"/>
       <c r="F63" s="1" t="s">
@@ -7313,7 +7316,7 @@
     <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="56"/>
       <c r="D64" s="74" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="E64" s="74"/>
       <c r="F64" s="1" t="s">
@@ -7333,7 +7336,7 @@
     <row r="65" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C65" s="56"/>
       <c r="D65" s="74" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="E65" s="74"/>
       <c r="F65" s="1" t="s">
@@ -7353,7 +7356,7 @@
     <row r="66" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C66" s="56"/>
       <c r="D66" s="74" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="E66" s="74"/>
       <c r="F66" s="1" t="s">
@@ -7373,7 +7376,7 @@
     <row r="67" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C67" s="56"/>
       <c r="D67" s="74" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="E67" s="74"/>
       <c r="F67" s="1" t="s">
@@ -7428,8 +7431,8 @@
     </row>
     <row r="71" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C71" s="55"/>
-      <c r="D71" s="79"/>
-      <c r="E71" s="80"/>
+      <c r="D71" s="82"/>
+      <c r="E71" s="83"/>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
@@ -7452,8 +7455,8 @@
     </row>
     <row r="73" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C73" s="1"/>
-      <c r="D73" s="79"/>
-      <c r="E73" s="80"/>
+      <c r="D73" s="82"/>
+      <c r="E73" s="83"/>
       <c r="F73" s="3"/>
       <c r="G73" s="4"/>
       <c r="H73" s="4"/>
@@ -7464,8 +7467,8 @@
     </row>
     <row r="74" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C74" s="1"/>
-      <c r="D74" s="79"/>
-      <c r="E74" s="80"/>
+      <c r="D74" s="82"/>
+      <c r="E74" s="83"/>
       <c r="F74" s="14"/>
       <c r="G74" s="4">
         <f>SUM(G20:G72)</f>
@@ -7508,18 +7511,18 @@
       <c r="L76" s="90"/>
     </row>
     <row r="77" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C77" s="81" t="s">
+      <c r="C77" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D77" s="82"/>
-      <c r="E77" s="82"/>
-      <c r="F77" s="82"/>
-      <c r="G77" s="82"/>
-      <c r="H77" s="82"/>
-      <c r="I77" s="82"/>
-      <c r="J77" s="82"/>
-      <c r="K77" s="82"/>
-      <c r="L77" s="83"/>
+      <c r="D77" s="76"/>
+      <c r="E77" s="76"/>
+      <c r="F77" s="76"/>
+      <c r="G77" s="76"/>
+      <c r="H77" s="76"/>
+      <c r="I77" s="76"/>
+      <c r="J77" s="76"/>
+      <c r="K77" s="76"/>
+      <c r="L77" s="77"/>
     </row>
     <row r="78" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C78" s="6" t="s">
@@ -7571,7 +7574,7 @@
         <v>649</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="F80" s="1"/>
       <c r="G80" s="1"/>
@@ -7584,7 +7587,7 @@
     <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="27"/>
       <c r="D81" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>649</v>
@@ -7683,7 +7686,7 @@
         <v>643</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F87" s="1"/>
       <c r="G87" s="1"/>
@@ -7696,7 +7699,7 @@
     <row r="88" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C88" s="27"/>
       <c r="D88" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>643</v>
@@ -7851,9 +7854,9 @@
         <v>0</v>
       </c>
       <c r="I99" s="3"/>
-      <c r="J99" s="75"/>
-      <c r="K99" s="75"/>
-      <c r="L99" s="75"/>
+      <c r="J99" s="78"/>
+      <c r="K99" s="78"/>
+      <c r="L99" s="78"/>
     </row>
     <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D100" s="38"/>
@@ -8083,11 +8086,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -8284,13 +8287,13 @@
       <c r="J12" s="89"/>
       <c r="K12" s="89"/>
       <c r="L12" s="89"/>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="83"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="77"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C13" s="90"/>
@@ -8312,10 +8315,10 @@
       <c r="P13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="77" t="s">
+      <c r="Q13" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R13" s="78"/>
+      <c r="R13" s="81"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C14" s="96" t="s">
@@ -8354,13 +8357,13 @@
         <v>53</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J15" s="88" t="s">
         <v>7</v>
       </c>
       <c r="K15" s="88"/>
-      <c r="L15" s="78"/>
+      <c r="L15" s="81"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
       <c r="P15" s="3"/>
@@ -8370,11 +8373,11 @@
     <row r="16" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C16" s="55"/>
       <c r="D16" s="74" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="E16" s="74"/>
       <c r="F16" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="G16" s="1">
         <v>10</v>
@@ -8393,11 +8396,11 @@
     <row r="17" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C17" s="55"/>
       <c r="D17" s="74" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="E17" s="74"/>
       <c r="F17" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G17" s="1">
         <v>24</v>
@@ -8416,11 +8419,11 @@
     <row r="18" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C18" s="56"/>
       <c r="D18" s="74" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="E18" s="74"/>
       <c r="F18" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="G18" s="1">
         <v>12</v>
@@ -8439,11 +8442,11 @@
     <row r="19" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C19" s="56"/>
       <c r="D19" s="74" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="E19" s="74"/>
       <c r="F19" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G19" s="1">
         <v>6</v>
@@ -8466,7 +8469,7 @@
       </c>
       <c r="E20" s="74"/>
       <c r="F20" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G20" s="1">
         <v>11</v>
@@ -8485,11 +8488,11 @@
     <row r="21" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C21" s="56"/>
       <c r="D21" s="74" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="E21" s="74"/>
       <c r="F21" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="G21" s="1">
         <v>22</v>
@@ -8514,11 +8517,11 @@
     <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="56"/>
       <c r="D22" s="74" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E22" s="74"/>
       <c r="F22" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G22" s="1">
         <v>14</v>
@@ -8537,11 +8540,11 @@
     <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="56"/>
       <c r="D23" s="74" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="E23" s="74"/>
       <c r="F23" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G23" s="1">
         <v>7.9</v>
@@ -8560,11 +8563,11 @@
     <row r="24" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C24" s="56"/>
       <c r="D24" s="74" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="E24" s="74"/>
       <c r="F24" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G24" s="1">
         <v>2.5</v>
@@ -8574,22 +8577,22 @@
       <c r="J24" s="74"/>
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
-      <c r="N24" s="81" t="s">
+      <c r="N24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O24" s="82"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="56"/>
       <c r="D25" s="74" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="E25" s="74"/>
       <c r="F25" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G25" s="1">
         <v>14</v>
@@ -8608,7 +8611,7 @@
       <c r="P25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q25" s="77" t="s">
+      <c r="Q25" s="80" t="s">
         <v>7</v>
       </c>
       <c r="R25" s="88"/>
@@ -8616,11 +8619,11 @@
     <row r="26" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C26" s="56"/>
       <c r="D26" s="74" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="E26" s="74"/>
       <c r="F26" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G26" s="1">
         <v>10</v>
@@ -8639,11 +8642,11 @@
     <row r="27" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C27" s="56"/>
       <c r="D27" s="74" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="E27" s="74"/>
       <c r="F27" s="1" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="G27" s="1">
         <v>6</v>
@@ -8662,11 +8665,11 @@
     <row r="28" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C28" s="56"/>
       <c r="D28" s="74" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="E28" s="74"/>
       <c r="F28" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G28" s="1">
         <v>6</v>
@@ -8688,11 +8691,11 @@
     <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="56"/>
       <c r="D29" s="74" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="E29" s="74"/>
       <c r="F29" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G29" s="1">
         <v>6</v>
@@ -8711,11 +8714,11 @@
     <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="56"/>
       <c r="D30" s="74" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="E30" s="74"/>
       <c r="F30" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G30" s="1">
         <v>6</v>
@@ -8734,11 +8737,11 @@
     <row r="31" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C31" s="56"/>
       <c r="D31" s="74" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="E31" s="74"/>
       <c r="F31" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G31" s="1">
         <v>6</v>
@@ -8748,22 +8751,22 @@
       <c r="J31" s="74"/>
       <c r="K31" s="74"/>
       <c r="L31" s="74"/>
-      <c r="N31" s="81" t="s">
+      <c r="N31" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="83"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="77"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="56"/>
       <c r="D32" s="74" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E32" s="74"/>
       <c r="F32" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G32" s="1">
         <v>10</v>
@@ -8793,11 +8796,11 @@
     <row r="33" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C33" s="55"/>
       <c r="D33" s="74" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="E33" s="74"/>
       <c r="F33" s="3" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G33" s="4">
         <v>5.5</v>
@@ -8848,17 +8851,17 @@
       <c r="J36" s="74"/>
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
-      <c r="N36" s="81" t="s">
+      <c r="N36" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="83"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="56"/>
-      <c r="D37" s="79"/>
-      <c r="E37" s="80"/>
+      <c r="D37" s="82"/>
+      <c r="E37" s="83"/>
       <c r="F37" s="1"/>
       <c r="G37" s="1"/>
       <c r="H37" s="57"/>
@@ -8881,8 +8884,8 @@
     </row>
     <row r="38" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C38" s="55"/>
-      <c r="D38" s="79"/>
-      <c r="E38" s="80"/>
+      <c r="D38" s="82"/>
+      <c r="E38" s="83"/>
       <c r="F38" s="1"/>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
@@ -8919,8 +8922,8 @@
     </row>
     <row r="40" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="80"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="83"/>
       <c r="F40" s="3"/>
       <c r="G40" s="4"/>
       <c r="H40" s="4"/>
@@ -8931,8 +8934,8 @@
     </row>
     <row r="41" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C41" s="1"/>
-      <c r="D41" s="79"/>
-      <c r="E41" s="80"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="83"/>
       <c r="F41" s="14"/>
       <c r="G41" s="4">
         <f>SUM(G16:G39)</f>
@@ -8975,18 +8978,18 @@
       <c r="L43" s="90"/>
     </row>
     <row r="44" spans="3:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="C44" s="81" t="s">
+      <c r="C44" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D44" s="82"/>
-      <c r="E44" s="82"/>
-      <c r="F44" s="82"/>
-      <c r="G44" s="82"/>
-      <c r="H44" s="82"/>
-      <c r="I44" s="82"/>
-      <c r="J44" s="82"/>
-      <c r="K44" s="82"/>
-      <c r="L44" s="83"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
+      <c r="I44" s="76"/>
+      <c r="J44" s="76"/>
+      <c r="K44" s="76"/>
+      <c r="L44" s="77"/>
     </row>
     <row r="45" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C45" s="6" t="s">
@@ -9198,9 +9201,9 @@
         <v>0</v>
       </c>
       <c r="I60" s="3"/>
-      <c r="J60" s="75"/>
-      <c r="K60" s="75"/>
-      <c r="L60" s="75"/>
+      <c r="J60" s="78"/>
+      <c r="K60" s="78"/>
+      <c r="L60" s="78"/>
     </row>
     <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D61" s="38"/>
@@ -9359,11 +9362,11 @@
       <c r="I2" s="97"/>
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
-      <c r="M2" s="81" t="s">
+      <c r="M2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="N2" s="82"/>
-      <c r="O2" s="83"/>
+      <c r="N2" s="76"/>
+      <c r="O2" s="77"/>
     </row>
     <row r="3" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B3" s="6" t="s">
@@ -10010,11 +10013,11 @@
       <c r="O21" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="P21" s="76" t="s">
+      <c r="P21" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="Q21" s="76"/>
-      <c r="R21" s="76"/>
+      <c r="Q21" s="79"/>
+      <c r="R21" s="79"/>
     </row>
     <row r="22" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B22" s="2">
@@ -10048,11 +10051,11 @@
       <c r="O22" s="3">
         <v>45784</v>
       </c>
-      <c r="P22" s="75" t="s">
+      <c r="P22" s="78" t="s">
         <v>40</v>
       </c>
-      <c r="Q22" s="75"/>
-      <c r="R22" s="75"/>
+      <c r="Q22" s="78"/>
+      <c r="R22" s="78"/>
     </row>
     <row r="23" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B23" s="2">
@@ -10086,11 +10089,11 @@
       <c r="O23" s="3">
         <v>37988</v>
       </c>
-      <c r="P23" s="75" t="s">
+      <c r="P23" s="78" t="s">
         <v>42</v>
       </c>
-      <c r="Q23" s="75"/>
-      <c r="R23" s="75"/>
+      <c r="Q23" s="78"/>
+      <c r="R23" s="78"/>
     </row>
     <row r="24" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B24" s="2">
@@ -10557,11 +10560,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -10585,12 +10588,12 @@
       <c r="G3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="H3" s="77" t="s">
+      <c r="H3" s="80" t="s">
         <v>7</v>
       </c>
       <c r="I3" s="88"/>
       <c r="J3" s="88"/>
-      <c r="K3" s="78"/>
+      <c r="K3" s="81"/>
       <c r="L3" s="6" t="s">
         <v>5</v>
       </c>
@@ -10816,13 +10819,13 @@
       <c r="J10" s="105"/>
       <c r="K10" s="105"/>
       <c r="L10" s="105"/>
-      <c r="N10" s="81" t="s">
+      <c r="N10" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O10" s="82"/>
-      <c r="P10" s="82"/>
-      <c r="Q10" s="82"/>
-      <c r="R10" s="83"/>
+      <c r="O10" s="76"/>
+      <c r="P10" s="76"/>
+      <c r="Q10" s="76"/>
+      <c r="R10" s="77"/>
       <c r="T10">
         <v>204.66</v>
       </c>
@@ -10848,10 +10851,10 @@
       <c r="P11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="77" t="s">
+      <c r="Q11" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R11" s="78"/>
+      <c r="R11" s="81"/>
       <c r="T11">
         <v>295.75</v>
       </c>
@@ -10907,12 +10910,12 @@
       <c r="H13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="I13" s="77" t="s">
+      <c r="I13" s="80" t="s">
         <v>7</v>
       </c>
       <c r="J13" s="88"/>
       <c r="K13" s="88"/>
-      <c r="L13" s="78"/>
+      <c r="L13" s="81"/>
       <c r="N13" s="3" t="s">
         <v>288</v>
       </c>
@@ -11016,10 +11019,10 @@
         <v>400</v>
       </c>
       <c r="H16" s="1"/>
-      <c r="I16" s="79"/>
+      <c r="I16" s="82"/>
       <c r="J16" s="109"/>
       <c r="K16" s="109"/>
-      <c r="L16" s="80"/>
+      <c r="L16" s="83"/>
       <c r="N16" s="3" t="s">
         <v>304</v>
       </c>
@@ -11055,10 +11058,10 @@
         <v>300</v>
       </c>
       <c r="H17" s="1"/>
-      <c r="I17" s="79"/>
+      <c r="I17" s="82"/>
       <c r="J17" s="109"/>
       <c r="K17" s="109"/>
-      <c r="L17" s="80"/>
+      <c r="L17" s="83"/>
       <c r="N17" s="3" t="s">
         <v>402</v>
       </c>
@@ -11092,10 +11095,10 @@
       <c r="H18" s="1">
         <v>653.15</v>
       </c>
-      <c r="I18" s="79"/>
+      <c r="I18" s="82"/>
       <c r="J18" s="109"/>
       <c r="K18" s="109"/>
-      <c r="L18" s="80"/>
+      <c r="L18" s="83"/>
       <c r="N18" s="3"/>
       <c r="O18" s="4">
         <f>SUM(O12:O17)</f>
@@ -11131,10 +11134,10 @@
         <v>400</v>
       </c>
       <c r="H19" s="1"/>
-      <c r="I19" s="79"/>
+      <c r="I19" s="82"/>
       <c r="J19" s="109"/>
       <c r="K19" s="109"/>
-      <c r="L19" s="80"/>
+      <c r="L19" s="83"/>
       <c r="N19" s="89"/>
       <c r="O19" s="89"/>
       <c r="P19" s="89"/>
@@ -11164,10 +11167,10 @@
         <v>300</v>
       </c>
       <c r="H20" s="1"/>
-      <c r="I20" s="79"/>
+      <c r="I20" s="82"/>
       <c r="J20" s="109"/>
       <c r="K20" s="109"/>
-      <c r="L20" s="80"/>
+      <c r="L20" s="83"/>
       <c r="N20" s="90"/>
       <c r="O20" s="90"/>
       <c r="P20" s="90"/>
@@ -11199,10 +11202,10 @@
       <c r="H21" s="1">
         <v>914.32</v>
       </c>
-      <c r="I21" s="79"/>
+      <c r="I21" s="82"/>
       <c r="J21" s="109"/>
       <c r="K21" s="109"/>
-      <c r="L21" s="80"/>
+      <c r="L21" s="83"/>
       <c r="N21" s="97" t="s">
         <v>38</v>
       </c>
@@ -11286,8 +11289,8 @@
       <c r="P23" s="3">
         <v>23763</v>
       </c>
-      <c r="Q23" s="75"/>
-      <c r="R23" s="75"/>
+      <c r="Q23" s="78"/>
+      <c r="R23" s="78"/>
       <c r="T23">
         <v>1615.21</v>
       </c>
@@ -11325,8 +11328,8 @@
       <c r="P24" s="3">
         <v>23763</v>
       </c>
-      <c r="Q24" s="75"/>
-      <c r="R24" s="75"/>
+      <c r="Q24" s="78"/>
+      <c r="R24" s="78"/>
       <c r="T24">
         <v>192.43</v>
       </c>
@@ -11353,18 +11356,18 @@
       <c r="H25" s="1">
         <v>2000.76</v>
       </c>
-      <c r="I25" s="79"/>
+      <c r="I25" s="82"/>
       <c r="J25" s="109"/>
       <c r="K25" s="109"/>
-      <c r="L25" s="80"/>
+      <c r="L25" s="83"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
       <c r="P25" s="5">
         <f>SUM(P23:P24)</f>
         <v>47526</v>
       </c>
-      <c r="Q25" s="75"/>
-      <c r="R25" s="75"/>
+      <c r="Q25" s="78"/>
+      <c r="R25" s="78"/>
       <c r="T25">
         <v>301.61</v>
       </c>
@@ -11641,10 +11644,10 @@
       <c r="J33" s="74"/>
       <c r="K33" s="74"/>
       <c r="L33" s="74"/>
-      <c r="N33" s="81" t="s">
+      <c r="N33" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O33" s="83"/>
+      <c r="O33" s="77"/>
       <c r="T33">
         <v>785.51</v>
       </c>
@@ -11667,10 +11670,10 @@
         <v>800</v>
       </c>
       <c r="H34" s="1"/>
-      <c r="I34" s="79"/>
+      <c r="I34" s="82"/>
       <c r="J34" s="109"/>
       <c r="K34" s="109"/>
-      <c r="L34" s="80"/>
+      <c r="L34" s="83"/>
       <c r="N34" s="6" t="s">
         <v>63</v>
       </c>
@@ -11699,10 +11702,10 @@
         <v>1300</v>
       </c>
       <c r="H35" s="1"/>
-      <c r="I35" s="79"/>
+      <c r="I35" s="82"/>
       <c r="J35" s="109"/>
       <c r="K35" s="109"/>
-      <c r="L35" s="80"/>
+      <c r="L35" s="83"/>
       <c r="N35" s="5">
         <f>G9+O7+P18+P25+H57+R30+H112</f>
         <v>187497.72</v>
@@ -12329,19 +12332,19 @@
       <c r="L59" s="107"/>
     </row>
     <row r="60" spans="2:21" ht="19" x14ac:dyDescent="0.25">
-      <c r="B60" s="81" t="s">
+      <c r="B60" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="C60" s="82"/>
-      <c r="D60" s="82"/>
-      <c r="E60" s="82"/>
-      <c r="F60" s="82"/>
-      <c r="G60" s="82"/>
-      <c r="H60" s="82"/>
-      <c r="I60" s="82"/>
-      <c r="J60" s="82"/>
-      <c r="K60" s="82"/>
-      <c r="L60" s="82"/>
+      <c r="C60" s="76"/>
+      <c r="D60" s="76"/>
+      <c r="E60" s="76"/>
+      <c r="F60" s="76"/>
+      <c r="G60" s="76"/>
+      <c r="H60" s="76"/>
+      <c r="I60" s="76"/>
+      <c r="J60" s="76"/>
+      <c r="K60" s="76"/>
+      <c r="L60" s="76"/>
     </row>
     <row r="61" spans="2:21" ht="19" x14ac:dyDescent="0.25">
       <c r="B61" s="6" t="s">
@@ -13728,11 +13731,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -14031,13 +14034,13 @@
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="N10" s="81" t="s">
+      <c r="N10" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O10" s="82"/>
-      <c r="P10" s="82"/>
-      <c r="Q10" s="82"/>
-      <c r="R10" s="83"/>
+      <c r="O10" s="76"/>
+      <c r="P10" s="76"/>
+      <c r="Q10" s="76"/>
+      <c r="R10" s="77"/>
     </row>
     <row r="11" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B11" s="13"/>
@@ -14060,10 +14063,10 @@
       <c r="P11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q11" s="77" t="s">
+      <c r="Q11" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R11" s="78"/>
+      <c r="R11" s="81"/>
     </row>
     <row r="12" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B12" s="2"/>
@@ -14195,12 +14198,12 @@
       <c r="H16" s="12" t="s">
         <v>53</v>
       </c>
-      <c r="I16" s="77" t="s">
+      <c r="I16" s="80" t="s">
         <v>7</v>
       </c>
       <c r="J16" s="88"/>
       <c r="K16" s="88"/>
-      <c r="L16" s="78"/>
+      <c r="L16" s="81"/>
       <c r="N16" s="18" t="s">
         <v>455</v>
       </c>
@@ -14476,13 +14479,13 @@
       <c r="J25" s="124"/>
       <c r="K25" s="124"/>
       <c r="L25" s="125"/>
-      <c r="N25" s="81" t="s">
+      <c r="N25" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O25" s="82"/>
-      <c r="P25" s="82"/>
-      <c r="Q25" s="82"/>
-      <c r="R25" s="82"/>
+      <c r="O25" s="76"/>
+      <c r="P25" s="76"/>
+      <c r="Q25" s="76"/>
+      <c r="R25" s="76"/>
     </row>
     <row r="26" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C26" s="43">
@@ -14514,7 +14517,7 @@
       <c r="P26" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q26" s="77" t="s">
+      <c r="Q26" s="80" t="s">
         <v>7</v>
       </c>
       <c r="R26" s="88"/>
@@ -15851,18 +15854,18 @@
       <c r="L84" s="90"/>
     </row>
     <row r="85" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C85" s="81" t="s">
+      <c r="C85" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D85" s="82"/>
-      <c r="E85" s="82"/>
-      <c r="F85" s="82"/>
-      <c r="G85" s="82"/>
-      <c r="H85" s="82"/>
-      <c r="I85" s="82"/>
-      <c r="J85" s="82"/>
-      <c r="K85" s="82"/>
-      <c r="L85" s="83"/>
+      <c r="D85" s="76"/>
+      <c r="E85" s="76"/>
+      <c r="F85" s="76"/>
+      <c r="G85" s="76"/>
+      <c r="H85" s="76"/>
+      <c r="I85" s="76"/>
+      <c r="J85" s="76"/>
+      <c r="K85" s="76"/>
+      <c r="L85" s="77"/>
     </row>
     <row r="86" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C86" s="6" t="s">
@@ -15886,11 +15889,11 @@
       <c r="I86" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="J86" s="76" t="s">
+      <c r="J86" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="K86" s="76"/>
-      <c r="L86" s="76"/>
+      <c r="K86" s="79"/>
+      <c r="L86" s="79"/>
     </row>
     <row r="87" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C87" s="39">
@@ -16428,9 +16431,9 @@
         <v>11183.16</v>
       </c>
       <c r="I110" s="3"/>
-      <c r="J110" s="75"/>
-      <c r="K110" s="75"/>
-      <c r="L110" s="75"/>
+      <c r="J110" s="78"/>
+      <c r="K110" s="78"/>
+      <c r="L110" s="78"/>
     </row>
     <row r="111" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D111" s="38"/>
@@ -16683,11 +16686,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -16746,15 +16749,17 @@
         <v>660</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>686</v>
+        <v>879</v>
       </c>
       <c r="F4" s="3">
-        <v>83.43</v>
-      </c>
-      <c r="G4" s="3"/>
+        <v>79.62</v>
+      </c>
+      <c r="G4" s="3">
+        <v>8897</v>
+      </c>
       <c r="H4" s="50">
         <f>F4/L4</f>
-        <v>41.715000000000003</v>
+        <v>39.81</v>
       </c>
       <c r="I4" s="93"/>
       <c r="J4" s="94"/>
@@ -16782,7 +16787,7 @@
         <v>674</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="F5" s="3">
         <v>79.73</v>
@@ -16795,7 +16800,7 @@
         <v>39.865000000000002</v>
       </c>
       <c r="I5" s="93" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="J5" s="94"/>
       <c r="K5" s="94"/>
@@ -16822,7 +16827,7 @@
         <v>659</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="F6" s="3">
         <v>121.36</v>
@@ -16860,7 +16865,7 @@
         <v>658</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="F7" s="3">
         <v>178.75</v>
@@ -16880,10 +16885,10 @@
         <v>4</v>
       </c>
       <c r="N7" s="3" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="O7" s="3">
-        <v>250</v>
+        <v>350</v>
       </c>
       <c r="P7" s="1"/>
     </row>
@@ -16900,7 +16905,7 @@
       <c r="K8" s="95"/>
       <c r="L8" s="3"/>
       <c r="N8" s="3" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="O8" s="3">
         <v>1750</v>
@@ -16914,15 +16919,15 @@
       <c r="E9" s="3"/>
       <c r="F9" s="3">
         <f>SUM(F4:F7)</f>
-        <v>463.27000000000004</v>
+        <v>459.46000000000004</v>
       </c>
       <c r="G9" s="5">
         <f>SUM(G4:G7)</f>
-        <v>41264</v>
+        <v>50161</v>
       </c>
       <c r="H9" s="50">
         <f>F9/L9</f>
-        <v>42.115454545454547</v>
+        <v>41.769090909090913</v>
       </c>
       <c r="I9" s="95"/>
       <c r="J9" s="95"/>
@@ -16934,7 +16939,7 @@
       <c r="N9" s="1"/>
       <c r="O9" s="5">
         <f>SUM(O4:O8)</f>
-        <v>14640</v>
+        <v>14740</v>
       </c>
       <c r="P9" s="1"/>
     </row>
@@ -16976,13 +16981,13 @@
       <c r="J12" s="96"/>
       <c r="K12" s="96"/>
       <c r="L12" s="96"/>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="83"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="77"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C13" s="12" t="s">
@@ -17002,13 +17007,13 @@
         <v>53</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J13" s="88" t="s">
         <v>7</v>
       </c>
       <c r="K13" s="88"/>
-      <c r="L13" s="78"/>
+      <c r="L13" s="81"/>
       <c r="N13" s="6" t="s">
         <v>45</v>
       </c>
@@ -17018,19 +17023,19 @@
       <c r="P13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="77" t="s">
+      <c r="Q13" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R13" s="78"/>
+      <c r="R13" s="81"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C14" s="55">
         <v>46177</v>
       </c>
-      <c r="D14" s="79" t="s">
+      <c r="D14" s="82" t="s">
         <v>670</v>
       </c>
-      <c r="E14" s="80"/>
+      <c r="E14" s="83"/>
       <c r="F14" s="1" t="s">
         <v>660</v>
       </c>
@@ -17042,7 +17047,7 @@
         <v>20</v>
       </c>
       <c r="J14" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K14" s="103"/>
       <c r="L14" s="104"/>
@@ -17060,10 +17065,10 @@
       <c r="C15" s="55">
         <v>46177</v>
       </c>
-      <c r="D15" s="79" t="s">
-        <v>848</v>
-      </c>
-      <c r="E15" s="80"/>
+      <c r="D15" s="82" t="s">
+        <v>847</v>
+      </c>
+      <c r="E15" s="83"/>
       <c r="F15" s="1" t="s">
         <v>660</v>
       </c>
@@ -17075,20 +17080,22 @@
         <v>12</v>
       </c>
       <c r="J15" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K15" s="103"/>
       <c r="L15" s="104"/>
       <c r="N15" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="O15" s="3">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="P15" s="3">
-        <v>14512</v>
-      </c>
-      <c r="Q15" s="84"/>
+        <v>15642</v>
+      </c>
+      <c r="Q15" s="84" t="s">
+        <v>878</v>
+      </c>
       <c r="R15" s="85"/>
     </row>
     <row r="16" spans="2:18" ht="19" x14ac:dyDescent="0.25">
@@ -17110,7 +17117,7 @@
         <v>19</v>
       </c>
       <c r="J16" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K16" s="103"/>
       <c r="L16" s="104"/>
@@ -17131,7 +17138,7 @@
         <v>46177</v>
       </c>
       <c r="D17" s="67" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="E17" s="68"/>
       <c r="F17" s="57" t="s">
@@ -17145,12 +17152,12 @@
         <v>19</v>
       </c>
       <c r="J17" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K17" s="103"/>
       <c r="L17" s="104"/>
       <c r="N17" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="O17" s="3">
         <v>70</v>
@@ -17164,11 +17171,11 @@
         <v>46178</v>
       </c>
       <c r="D18" s="71" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="E18" s="71"/>
       <c r="F18" s="57" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G18" s="58">
         <v>18.899999999999999</v>
@@ -17181,7 +17188,7 @@
       <c r="K18" s="91"/>
       <c r="L18" s="68"/>
       <c r="N18" s="3" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="O18" s="4">
         <v>4.7</v>
@@ -17209,7 +17216,7 @@
         <v>3.5</v>
       </c>
       <c r="J19" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K19" s="103"/>
       <c r="L19" s="104"/>
@@ -17224,7 +17231,7 @@
         <v>46178</v>
       </c>
       <c r="D20" s="67" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E20" s="68"/>
       <c r="F20" s="57" t="s">
@@ -17238,7 +17245,7 @@
         <v>7.5</v>
       </c>
       <c r="J20" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K20" s="103"/>
       <c r="L20" s="104"/>
@@ -17267,18 +17274,18 @@
         <v>15</v>
       </c>
       <c r="J21" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K21" s="103"/>
       <c r="L21" s="104"/>
       <c r="N21" s="3"/>
       <c r="O21" s="15">
         <f>SUM(O14:O20)</f>
-        <v>289.08</v>
+        <v>299.08</v>
       </c>
       <c r="P21" s="5">
         <f>SUM(P14:P18)</f>
-        <v>15561</v>
+        <v>16691</v>
       </c>
       <c r="Q21" s="86"/>
       <c r="R21" s="87"/>
@@ -17315,7 +17322,7 @@
         <v>46179</v>
       </c>
       <c r="D23" s="71" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="E23" s="71"/>
       <c r="F23" s="57" t="s">
@@ -17358,17 +17365,17 @@
         <v>14.5</v>
       </c>
       <c r="J24" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K24" s="103"/>
       <c r="L24" s="104"/>
-      <c r="N24" s="81" t="s">
+      <c r="N24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O24" s="82"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="56">
@@ -17389,7 +17396,7 @@
         <v>17.5</v>
       </c>
       <c r="J25" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K25" s="103"/>
       <c r="L25" s="104"/>
@@ -17402,7 +17409,7 @@
       <c r="P25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q25" s="77" t="s">
+      <c r="Q25" s="80" t="s">
         <v>7</v>
       </c>
       <c r="R25" s="88"/>
@@ -17418,10 +17425,12 @@
       <c r="F26" s="57" t="s">
         <v>674</v>
       </c>
-      <c r="G26" s="57">
+      <c r="G26" s="58">
         <v>17.5</v>
       </c>
-      <c r="H26" s="57"/>
+      <c r="H26" s="57">
+        <v>1960</v>
+      </c>
       <c r="I26" s="57"/>
       <c r="J26" s="91"/>
       <c r="K26" s="91"/>
@@ -17430,7 +17439,7 @@
         <v>46176</v>
       </c>
       <c r="O26" s="3" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="P26" s="3">
         <v>25778</v>
@@ -17457,7 +17466,7 @@
         <v>20</v>
       </c>
       <c r="J27" s="103" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="K27" s="103"/>
       <c r="L27" s="104"/>
@@ -17465,7 +17474,7 @@
         <v>46188</v>
       </c>
       <c r="O27" s="3" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="P27" s="3">
         <v>25779</v>
@@ -17478,7 +17487,7 @@
         <v>46180</v>
       </c>
       <c r="D28" s="71" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="E28" s="71"/>
       <c r="F28" s="57" t="s">
@@ -17508,7 +17517,7 @@
         <v>46181</v>
       </c>
       <c r="D29" s="71" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="E29" s="71"/>
       <c r="F29" s="57" t="s">
@@ -17564,7 +17573,7 @@
         <v>46182</v>
       </c>
       <c r="D31" s="74" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="E31" s="74"/>
       <c r="F31" s="1" t="s">
@@ -17580,24 +17589,24 @@
       <c r="J31" s="91"/>
       <c r="K31" s="91"/>
       <c r="L31" s="68"/>
-      <c r="N31" s="81" t="s">
+      <c r="N31" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="83"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="77"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="55">
         <v>46182</v>
       </c>
-      <c r="D32" s="79" t="s">
+      <c r="D32" s="82" t="s">
         <v>666</v>
       </c>
-      <c r="E32" s="80"/>
+      <c r="E32" s="83"/>
       <c r="F32" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G32" s="58">
         <v>10</v>
@@ -17630,12 +17639,12 @@
       <c r="C33" s="55">
         <v>46182</v>
       </c>
-      <c r="D33" s="79" t="s">
+      <c r="D33" s="82" t="s">
         <v>667</v>
       </c>
-      <c r="E33" s="80"/>
+      <c r="E33" s="83"/>
       <c r="F33" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G33" s="1">
         <v>2</v>
@@ -17679,10 +17688,10 @@
       <c r="C35" s="55">
         <v>46183</v>
       </c>
-      <c r="D35" s="79" t="s">
-        <v>689</v>
-      </c>
-      <c r="E35" s="80"/>
+      <c r="D35" s="82" t="s">
+        <v>688</v>
+      </c>
+      <c r="E35" s="83"/>
       <c r="F35" s="1" t="s">
         <v>659</v>
       </c>
@@ -17700,7 +17709,7 @@
         <v>46183</v>
       </c>
       <c r="D36" s="74" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="E36" s="74"/>
       <c r="F36" s="1" t="s">
@@ -17716,19 +17725,19 @@
       </c>
       <c r="K36" s="91"/>
       <c r="L36" s="68"/>
-      <c r="N36" s="81" t="s">
+      <c r="N36" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="83"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="55">
         <v>46184</v>
       </c>
       <c r="D37" s="74" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="E37" s="74"/>
       <c r="F37" s="1" t="s">
@@ -17784,16 +17793,16 @@
       <c r="L38" s="73"/>
       <c r="N38" s="5">
         <f>(F9+O21+G61+G85)*R3+O9+P28</f>
-        <v>188455.08</v>
+        <v>189248.36</v>
       </c>
       <c r="O38" s="5">
         <f>G9+O9+P28+P21+H61+H85+R33</f>
-        <v>141742</v>
+        <v>153829</v>
       </c>
       <c r="P38" s="5"/>
       <c r="Q38" s="5">
         <f>P38+O38</f>
-        <v>141742</v>
+        <v>153829</v>
       </c>
     </row>
     <row r="39" spans="3:18" x14ac:dyDescent="0.2">
@@ -17826,7 +17835,7 @@
         <v>46184</v>
       </c>
       <c r="D40" s="71" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="E40" s="71"/>
       <c r="F40" s="57" t="s">
@@ -17850,7 +17859,7 @@
         <v>46184</v>
       </c>
       <c r="D41" s="71" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E41" s="71"/>
       <c r="F41" s="57" t="s">
@@ -17874,7 +17883,7 @@
         <v>46184</v>
       </c>
       <c r="D42" s="71" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="E42" s="71"/>
       <c r="F42" s="57" t="s">
@@ -17944,7 +17953,7 @@
         <v>46185</v>
       </c>
       <c r="D45" s="71" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E45" s="71"/>
       <c r="F45" s="57" t="s">
@@ -17992,7 +18001,7 @@
         <v>46185</v>
       </c>
       <c r="D47" s="71" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="E47" s="71"/>
       <c r="F47" s="57" t="s">
@@ -18004,7 +18013,7 @@
       <c r="H47" s="57"/>
       <c r="I47" s="57"/>
       <c r="J47" s="72" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K47" s="72"/>
       <c r="L47" s="73"/>
@@ -18014,11 +18023,11 @@
         <v>46186</v>
       </c>
       <c r="D48" s="74" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E48" s="74"/>
       <c r="F48" s="57" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G48" s="1">
         <v>6</v>
@@ -18034,11 +18043,11 @@
         <v>46186</v>
       </c>
       <c r="D49" s="74" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E49" s="74"/>
       <c r="F49" s="57" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G49" s="1">
         <v>6</v>
@@ -18054,11 +18063,11 @@
         <v>46186</v>
       </c>
       <c r="D50" s="74" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E50" s="74"/>
       <c r="F50" s="57" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G50" s="58">
         <v>16.5</v>
@@ -18080,7 +18089,7 @@
       </c>
       <c r="E51" s="74"/>
       <c r="F51" s="57" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G51" s="1">
         <v>12.5</v>
@@ -18096,11 +18105,11 @@
         <v>46186</v>
       </c>
       <c r="D52" s="74" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E52" s="74"/>
       <c r="F52" s="57" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="G52" s="1">
         <v>14.5</v>
@@ -18116,7 +18125,7 @@
         <v>46187</v>
       </c>
       <c r="D53" s="71" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E53" s="71"/>
       <c r="F53" s="57" t="s">
@@ -18128,7 +18137,7 @@
       <c r="H53" s="57"/>
       <c r="I53" s="57"/>
       <c r="J53" s="72" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="K53" s="72"/>
       <c r="L53" s="73"/>
@@ -18138,7 +18147,7 @@
         <v>46187</v>
       </c>
       <c r="D54" s="71" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E54" s="71"/>
       <c r="F54" s="57" t="s">
@@ -18150,7 +18159,7 @@
       <c r="H54" s="57"/>
       <c r="I54" s="57"/>
       <c r="J54" s="72" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="K54" s="72"/>
       <c r="L54" s="73"/>
@@ -18160,7 +18169,7 @@
         <v>46187</v>
       </c>
       <c r="D55" s="74" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="E55" s="74"/>
       <c r="F55" s="1" t="s">
@@ -18294,7 +18303,7 @@
       </c>
       <c r="H61" s="5">
         <f>SUM(H14:H59)</f>
-        <v>13671</v>
+        <v>15631</v>
       </c>
       <c r="I61" s="3">
         <f>SUM(I14:I59)</f>
@@ -18329,18 +18338,18 @@
       <c r="L63" s="90"/>
     </row>
     <row r="64" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C64" s="81" t="s">
+      <c r="C64" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D64" s="82"/>
-      <c r="E64" s="82"/>
-      <c r="F64" s="82"/>
-      <c r="G64" s="82"/>
-      <c r="H64" s="82"/>
-      <c r="I64" s="82"/>
-      <c r="J64" s="82"/>
-      <c r="K64" s="82"/>
-      <c r="L64" s="83"/>
+      <c r="D64" s="76"/>
+      <c r="E64" s="76"/>
+      <c r="F64" s="76"/>
+      <c r="G64" s="76"/>
+      <c r="H64" s="76"/>
+      <c r="I64" s="76"/>
+      <c r="J64" s="76"/>
+      <c r="K64" s="76"/>
+      <c r="L64" s="77"/>
     </row>
     <row r="65" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C65" s="6" t="s">
@@ -18364,18 +18373,18 @@
       <c r="I65" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="J65" s="76" t="s">
+      <c r="J65" s="79" t="s">
         <v>7</v>
       </c>
-      <c r="K65" s="76"/>
-      <c r="L65" s="76"/>
+      <c r="K65" s="79"/>
+      <c r="L65" s="79"/>
     </row>
     <row r="66" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C66" s="55">
         <v>46177</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>660</v>
@@ -18398,7 +18407,7 @@
         <v>660</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F67" s="1"/>
       <c r="G67" s="58">
@@ -18417,7 +18426,7 @@
         <v>46178</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>660</v>
@@ -18461,7 +18470,7 @@
         <v>6</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>685</v>
@@ -18481,7 +18490,7 @@
         <v>46180</v>
       </c>
       <c r="D71" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="E71" s="1"/>
       <c r="F71" s="1"/>
@@ -18564,7 +18573,7 @@
         <v>659</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F75" s="1"/>
       <c r="G75" s="1">
@@ -18581,7 +18590,7 @@
         <v>46182</v>
       </c>
       <c r="D76" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>659</v>
@@ -18624,7 +18633,7 @@
         <v>658</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F78" s="1"/>
       <c r="G78" s="58">
@@ -18643,7 +18652,7 @@
         <v>46186</v>
       </c>
       <c r="D79" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>658</v>
@@ -18705,11 +18714,19 @@
       <c r="L81" s="74"/>
     </row>
     <row r="82" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C82" s="1"/>
-      <c r="D82" s="1"/>
-      <c r="E82" s="1"/>
+      <c r="C82" s="55">
+        <v>46188</v>
+      </c>
+      <c r="D82" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>691</v>
+      </c>
       <c r="F82" s="1"/>
-      <c r="G82" s="1"/>
+      <c r="G82" s="1">
+        <v>5.0999999999999996</v>
+      </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
       <c r="J82" s="74"/>
@@ -18717,19 +18734,11 @@
       <c r="L82" s="74"/>
     </row>
     <row r="83" spans="3:12" x14ac:dyDescent="0.2">
-      <c r="C83" s="55">
-        <v>46188</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>658</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>692</v>
-      </c>
+      <c r="C83" s="55"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
       <c r="F83" s="1"/>
-      <c r="G83" s="1">
-        <v>5.0999999999999996</v>
-      </c>
+      <c r="G83" s="1"/>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
       <c r="J83" s="74"/>
@@ -18762,9 +18771,9 @@
         <v>5049</v>
       </c>
       <c r="I85" s="3"/>
-      <c r="J85" s="75"/>
-      <c r="K85" s="75"/>
-      <c r="L85" s="75"/>
+      <c r="J85" s="78"/>
+      <c r="K85" s="78"/>
+      <c r="L85" s="78"/>
     </row>
     <row r="86" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D86" s="38"/>
@@ -18798,14 +18807,7 @@
     <mergeCell ref="D53:E53"/>
     <mergeCell ref="J53:L53"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J40:L40"/>
     <mergeCell ref="J44:L44"/>
-    <mergeCell ref="J24:L24"/>
-    <mergeCell ref="J25:L25"/>
-    <mergeCell ref="J26:L26"/>
-    <mergeCell ref="J27:L27"/>
-    <mergeCell ref="J28:L28"/>
-    <mergeCell ref="J29:L29"/>
     <mergeCell ref="J13:L13"/>
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="J15:L15"/>
@@ -18878,6 +18880,13 @@
     <mergeCell ref="J35:L35"/>
     <mergeCell ref="J36:L36"/>
     <mergeCell ref="J37:L37"/>
+    <mergeCell ref="J40:L40"/>
+    <mergeCell ref="J24:L24"/>
+    <mergeCell ref="J25:L25"/>
+    <mergeCell ref="J26:L26"/>
+    <mergeCell ref="J27:L27"/>
+    <mergeCell ref="J28:L28"/>
+    <mergeCell ref="J29:L29"/>
     <mergeCell ref="Q13:R13"/>
     <mergeCell ref="D36:E36"/>
     <mergeCell ref="D35:E35"/>
@@ -18973,11 +18982,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -19221,13 +19230,13 @@
       <c r="J12" s="90"/>
       <c r="K12" s="90"/>
       <c r="L12" s="90"/>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="83"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="77"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C13" s="96" t="s">
@@ -19251,10 +19260,10 @@
       <c r="P13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="77" t="s">
+      <c r="Q13" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R13" s="78"/>
+      <c r="R13" s="81"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C14" s="12" t="s">
@@ -19274,15 +19283,15 @@
         <v>53</v>
       </c>
       <c r="I14" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J14" s="88" t="s">
         <v>7</v>
       </c>
       <c r="K14" s="88"/>
-      <c r="L14" s="78"/>
+      <c r="L14" s="81"/>
       <c r="N14" s="3" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="O14" s="3">
         <v>1419</v>
@@ -19561,13 +19570,13 @@
       </c>
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
-      <c r="N24" s="81" t="s">
+      <c r="N24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O24" s="82"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="56"/>
@@ -19599,7 +19608,7 @@
       <c r="P25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q25" s="77" t="s">
+      <c r="Q25" s="80" t="s">
         <v>7</v>
       </c>
       <c r="R25" s="88"/>
@@ -19759,13 +19768,13 @@
       </c>
       <c r="K31" s="74"/>
       <c r="L31" s="74"/>
-      <c r="N31" s="81" t="s">
+      <c r="N31" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="83"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="77"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="55"/>
@@ -19881,12 +19890,12 @@
       <c r="J36" s="74"/>
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
-      <c r="N36" s="81" t="s">
+      <c r="N36" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="83"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="55"/>
@@ -19903,7 +19912,7 @@
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
       <c r="J37" s="74" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K37" s="74"/>
       <c r="L37" s="74"/>
@@ -19960,8 +19969,8 @@
     </row>
     <row r="40" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C40" s="55"/>
-      <c r="D40" s="79"/>
-      <c r="E40" s="80"/>
+      <c r="D40" s="82"/>
+      <c r="E40" s="83"/>
       <c r="F40" s="1"/>
       <c r="G40" s="1"/>
       <c r="H40" s="1"/>
@@ -19984,8 +19993,8 @@
     </row>
     <row r="42" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C42" s="1"/>
-      <c r="D42" s="79"/>
-      <c r="E42" s="80"/>
+      <c r="D42" s="82"/>
+      <c r="E42" s="83"/>
       <c r="F42" s="3"/>
       <c r="G42" s="4"/>
       <c r="H42" s="4"/>
@@ -19996,8 +20005,8 @@
     </row>
     <row r="43" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C43" s="1"/>
-      <c r="D43" s="79"/>
-      <c r="E43" s="80"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="83"/>
       <c r="F43" s="14"/>
       <c r="G43" s="4">
         <f>SUM(G15:G41)</f>
@@ -20040,18 +20049,18 @@
       <c r="L45" s="90"/>
     </row>
     <row r="46" spans="3:18" ht="19" x14ac:dyDescent="0.25">
-      <c r="C46" s="81" t="s">
+      <c r="C46" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D46" s="82"/>
-      <c r="E46" s="82"/>
-      <c r="F46" s="82"/>
-      <c r="G46" s="82"/>
-      <c r="H46" s="82"/>
-      <c r="I46" s="82"/>
-      <c r="J46" s="82"/>
-      <c r="K46" s="82"/>
-      <c r="L46" s="83"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="76"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="76"/>
+      <c r="I46" s="76"/>
+      <c r="J46" s="76"/>
+      <c r="K46" s="76"/>
+      <c r="L46" s="77"/>
     </row>
     <row r="47" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C47" s="6" t="s">
@@ -20371,9 +20380,9 @@
         <v>0</v>
       </c>
       <c r="I62" s="3"/>
-      <c r="J62" s="75"/>
-      <c r="K62" s="75"/>
-      <c r="L62" s="75"/>
+      <c r="J62" s="78"/>
+      <c r="K62" s="78"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D63" s="38"/>
@@ -20412,8 +20421,6 @@
     <mergeCell ref="J42:L42"/>
     <mergeCell ref="D43:E43"/>
     <mergeCell ref="J43:L43"/>
-    <mergeCell ref="J30:L30"/>
-    <mergeCell ref="D31:E31"/>
     <mergeCell ref="J31:L31"/>
     <mergeCell ref="N29:R30"/>
     <mergeCell ref="D40:E40"/>
@@ -20427,8 +20434,6 @@
     <mergeCell ref="D38:E38"/>
     <mergeCell ref="J38:L38"/>
     <mergeCell ref="N31:R31"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="J22:L22"/>
     <mergeCell ref="Q27:R27"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="J23:L23"/>
@@ -20451,10 +20456,8 @@
     <mergeCell ref="J35:L35"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="N22:R23"/>
-    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="J30:L30"/>
+    <mergeCell ref="D31:E31"/>
     <mergeCell ref="J18:L18"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="J19:L19"/>
@@ -20462,6 +20465,8 @@
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="J24:L24"/>
     <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="J22:L22"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="J25:L25"/>
     <mergeCell ref="D26:E26"/>
@@ -20482,6 +20487,10 @@
     <mergeCell ref="J20:L20"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="J21:L21"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="N22:R23"/>
+    <mergeCell ref="D18:E18"/>
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="Q13:R13"/>
     <mergeCell ref="I9:K9"/>
@@ -20540,11 +20549,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -20789,13 +20798,13 @@
       <c r="J12" s="89"/>
       <c r="K12" s="89"/>
       <c r="L12" s="89"/>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="83"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="77"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C13" s="90"/>
@@ -20817,10 +20826,10 @@
       <c r="P13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="77" t="s">
+      <c r="Q13" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R13" s="78"/>
+      <c r="R13" s="81"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C14" s="96" t="s">
@@ -20863,13 +20872,13 @@
         <v>53</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J15" s="88" t="s">
         <v>7</v>
       </c>
       <c r="K15" s="88"/>
-      <c r="L15" s="78"/>
+      <c r="L15" s="81"/>
       <c r="N15" s="3" t="s">
         <v>481</v>
       </c>
@@ -21137,17 +21146,17 @@
         <v>60</v>
       </c>
       <c r="J24" s="74" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
-      <c r="N24" s="81" t="s">
+      <c r="N24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O24" s="82"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="56"/>
@@ -21166,7 +21175,7 @@
         <v>32.5</v>
       </c>
       <c r="J25" s="74" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K25" s="74"/>
       <c r="L25" s="74"/>
@@ -21179,7 +21188,7 @@
       <c r="P25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q25" s="77" t="s">
+      <c r="Q25" s="80" t="s">
         <v>7</v>
       </c>
       <c r="R25" s="88"/>
@@ -21201,7 +21210,7 @@
         <v>90</v>
       </c>
       <c r="J26" s="74" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K26" s="74"/>
       <c r="L26" s="74"/>
@@ -21312,7 +21321,7 @@
         <v>85</v>
       </c>
       <c r="J30" s="74" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K30" s="74"/>
       <c r="L30" s="74"/>
@@ -21339,17 +21348,17 @@
         <v>120</v>
       </c>
       <c r="J31" s="74" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K31" s="74"/>
       <c r="L31" s="74"/>
-      <c r="N31" s="81" t="s">
+      <c r="N31" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="83"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="77"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="55"/>
@@ -21406,7 +21415,7 @@
         <v>85</v>
       </c>
       <c r="J33" s="74" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K33" s="74"/>
       <c r="L33" s="74"/>
@@ -21475,16 +21484,16 @@
         <v>90</v>
       </c>
       <c r="J36" s="74" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
-      <c r="N36" s="81" t="s">
+      <c r="N36" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="83"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="55"/>
@@ -21641,15 +21650,15 @@
         <v>100</v>
       </c>
       <c r="J42" s="74" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="K42" s="74"/>
       <c r="L42" s="74"/>
     </row>
     <row r="43" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C43" s="56"/>
-      <c r="D43" s="79"/>
-      <c r="E43" s="80"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="83"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="57"/>
@@ -21660,8 +21669,8 @@
     </row>
     <row r="44" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C44" s="55"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="80"/>
+      <c r="D44" s="82"/>
+      <c r="E44" s="83"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1">
@@ -21688,8 +21697,8 @@
     </row>
     <row r="46" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="80"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="83"/>
       <c r="F46" s="3"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -21700,8 +21709,8 @@
     </row>
     <row r="47" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="80"/>
+      <c r="D47" s="82"/>
+      <c r="E47" s="83"/>
       <c r="F47" s="14"/>
       <c r="G47" s="4">
         <f>SUM(G16:G45)</f>
@@ -21744,18 +21753,18 @@
       <c r="L49" s="90"/>
     </row>
     <row r="50" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C50" s="81" t="s">
+      <c r="C50" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="82"/>
-      <c r="E50" s="82"/>
-      <c r="F50" s="82"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="82"/>
-      <c r="I50" s="82"/>
-      <c r="J50" s="82"/>
-      <c r="K50" s="82"/>
-      <c r="L50" s="83"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76"/>
+      <c r="J50" s="76"/>
+      <c r="K50" s="76"/>
+      <c r="L50" s="77"/>
     </row>
     <row r="51" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C51" s="6" t="s">
@@ -22107,9 +22116,9 @@
         <v>0</v>
       </c>
       <c r="I66" s="3"/>
-      <c r="J66" s="75"/>
-      <c r="K66" s="75"/>
-      <c r="L66" s="75"/>
+      <c r="J66" s="78"/>
+      <c r="K66" s="78"/>
+      <c r="L66" s="78"/>
     </row>
     <row r="67" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D67" s="38"/>
@@ -22186,8 +22195,6 @@
     <mergeCell ref="J36:L36"/>
     <mergeCell ref="N31:R31"/>
     <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="J23:L23"/>
     <mergeCell ref="Q28:R28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="J29:L29"/>
@@ -22195,8 +22202,8 @@
     <mergeCell ref="J30:L30"/>
     <mergeCell ref="Q25:R25"/>
     <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="J25:L25"/>
     <mergeCell ref="N22:R23"/>
     <mergeCell ref="D18:E18"/>
     <mergeCell ref="J18:L18"/>
@@ -22206,10 +22213,10 @@
     <mergeCell ref="Q20:R20"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="J24:L24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="J25:L25"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="J22:L22"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="J23:L23"/>
     <mergeCell ref="D16:E16"/>
     <mergeCell ref="J16:L16"/>
     <mergeCell ref="Q21:R21"/>
@@ -22226,6 +22233,8 @@
     <mergeCell ref="J20:L20"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="J21:L21"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="J17:L17"/>
     <mergeCell ref="I9:K9"/>
     <mergeCell ref="Q13:R13"/>
     <mergeCell ref="I10:K10"/>
@@ -22283,11 +22292,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -22600,13 +22609,13 @@
       <c r="J12" s="94"/>
       <c r="K12" s="108"/>
       <c r="L12" s="3"/>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="83"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="77"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B13" s="13"/>
@@ -22629,10 +22638,10 @@
       <c r="P13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="77" t="s">
+      <c r="Q13" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R13" s="78"/>
+      <c r="R13" s="81"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="B14" s="13"/>
@@ -22647,7 +22656,7 @@
       <c r="K14" s="115"/>
       <c r="L14" s="3"/>
       <c r="N14" s="3" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="O14" s="3">
         <v>27</v>
@@ -22681,7 +22690,7 @@
         <v>24</v>
       </c>
       <c r="N15" s="3" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="O15" s="3">
         <v>35</v>
@@ -22703,14 +22712,14 @@
       <c r="K16" s="89"/>
       <c r="L16" s="89"/>
       <c r="N16" s="3" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="O16" s="3">
         <v>28</v>
       </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="84" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="R16" s="85"/>
     </row>
@@ -22726,7 +22735,7 @@
       <c r="K17" s="90"/>
       <c r="L17" s="90"/>
       <c r="N17" s="3" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="O17" s="3">
         <v>85</v>
@@ -22749,7 +22758,7 @@
       <c r="K18" s="96"/>
       <c r="L18" s="96"/>
       <c r="N18" s="3" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="O18" s="3">
         <v>29</v>
@@ -22776,15 +22785,15 @@
         <v>53</v>
       </c>
       <c r="I19" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J19" s="88" t="s">
         <v>7</v>
       </c>
       <c r="K19" s="88"/>
-      <c r="L19" s="78"/>
+      <c r="L19" s="81"/>
       <c r="N19" s="3" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="O19" s="3">
         <v>26</v>
@@ -22796,7 +22805,7 @@
     <row r="20" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C20" s="55"/>
       <c r="D20" s="74" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="E20" s="74"/>
       <c r="F20" s="1" t="s">
@@ -22819,7 +22828,7 @@
     <row r="21" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C21" s="55"/>
       <c r="D21" s="74" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="E21" s="74"/>
       <c r="F21" s="1" t="s">
@@ -22860,7 +22869,7 @@
       <c r="H22" s="57"/>
       <c r="I22" s="1"/>
       <c r="J22" s="74" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="K22" s="74"/>
       <c r="L22" s="74"/>
@@ -22873,7 +22882,7 @@
     <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="56"/>
       <c r="D23" s="74" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="E23" s="74"/>
       <c r="F23" s="1" t="s">
@@ -22908,17 +22917,17 @@
       <c r="H24" s="57"/>
       <c r="I24" s="1"/>
       <c r="J24" s="74" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
-      <c r="N24" s="81" t="s">
+      <c r="N24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O24" s="82"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="56"/>
@@ -22946,19 +22955,19 @@
       <c r="P25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q25" s="77" t="s">
+      <c r="Q25" s="80" t="s">
         <v>7</v>
       </c>
       <c r="R25" s="88"/>
     </row>
     <row r="26" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C26" s="56"/>
-      <c r="D26" s="79" t="s">
-        <v>711</v>
-      </c>
-      <c r="E26" s="80"/>
+      <c r="D26" s="82" t="s">
+        <v>710</v>
+      </c>
+      <c r="E26" s="83"/>
       <c r="F26" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="G26" s="1">
         <v>25</v>
@@ -22977,11 +22986,11 @@
     <row r="27" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C27" s="56"/>
       <c r="D27" s="74" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E27" s="74"/>
       <c r="F27" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="G27" s="1">
         <v>15</v>
@@ -23014,7 +23023,7 @@
         <v>10</v>
       </c>
       <c r="J28" s="74" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K28" s="74"/>
       <c r="L28" s="74"/>
@@ -23030,7 +23039,7 @@
     <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="56"/>
       <c r="D29" s="74" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E29" s="74"/>
       <c r="F29" s="1" t="s">
@@ -23044,7 +23053,7 @@
         <v>8</v>
       </c>
       <c r="J29" s="74" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K29" s="74"/>
       <c r="L29" s="74"/>
@@ -23057,7 +23066,7 @@
     <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="56"/>
       <c r="D30" s="74" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="E30" s="74"/>
       <c r="F30" s="1" t="s">
@@ -23071,7 +23080,7 @@
         <v>9</v>
       </c>
       <c r="J30" s="74" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K30" s="74"/>
       <c r="L30" s="74"/>
@@ -23084,7 +23093,7 @@
     <row r="31" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C31" s="56"/>
       <c r="D31" s="74" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="E31" s="74"/>
       <c r="F31" s="1" t="s">
@@ -23098,22 +23107,22 @@
         <v>9</v>
       </c>
       <c r="J31" s="74" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K31" s="74"/>
       <c r="L31" s="74"/>
-      <c r="N31" s="81" t="s">
+      <c r="N31" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="83"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="77"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="56"/>
       <c r="D32" s="74" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="E32" s="74"/>
       <c r="F32" s="1" t="s">
@@ -23127,7 +23136,7 @@
         <v>6</v>
       </c>
       <c r="J32" s="74" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="K32" s="74"/>
       <c r="L32" s="74"/>
@@ -23151,7 +23160,7 @@
     <row r="33" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C33" s="56"/>
       <c r="D33" s="74" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="E33" s="74"/>
       <c r="F33" s="1" t="s">
@@ -23165,7 +23174,7 @@
         <v>10</v>
       </c>
       <c r="J33" s="74" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K33" s="74"/>
       <c r="L33" s="74"/>
@@ -23178,7 +23187,7 @@
     <row r="34" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C34" s="56"/>
       <c r="D34" s="74" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="E34" s="74"/>
       <c r="F34" s="1" t="s">
@@ -23196,7 +23205,7 @@
     <row r="35" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C35" s="56"/>
       <c r="D35" s="74" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="E35" s="74"/>
       <c r="F35" s="1" t="s">
@@ -23210,7 +23219,7 @@
         <v>8</v>
       </c>
       <c r="J35" s="74" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K35" s="74"/>
       <c r="L35" s="74"/>
@@ -23218,7 +23227,7 @@
     <row r="36" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C36" s="56"/>
       <c r="D36" s="74" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E36" s="74"/>
       <c r="F36" s="1" t="s">
@@ -23232,21 +23241,21 @@
         <v>16</v>
       </c>
       <c r="J36" s="74" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
-      <c r="N36" s="81" t="s">
+      <c r="N36" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="83"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="55"/>
       <c r="D37" s="74" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E37" s="74"/>
       <c r="F37" s="1" t="s">
@@ -23260,7 +23269,7 @@
         <v>18</v>
       </c>
       <c r="J37" s="74" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="K37" s="74"/>
       <c r="L37" s="74"/>
@@ -23280,7 +23289,7 @@
     <row r="38" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C38" s="55"/>
       <c r="D38" s="74" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="E38" s="74"/>
       <c r="F38" s="1" t="s">
@@ -23294,7 +23303,7 @@
         <v>10</v>
       </c>
       <c r="J38" s="74" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="K38" s="74"/>
       <c r="L38" s="74"/>
@@ -23315,7 +23324,7 @@
     <row r="39" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C39" s="55"/>
       <c r="D39" s="74" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="E39" s="74"/>
       <c r="F39" s="1" t="s">
@@ -23329,7 +23338,7 @@
         <v>12</v>
       </c>
       <c r="J39" s="74" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K39" s="74"/>
       <c r="L39" s="74"/>
@@ -23338,7 +23347,7 @@
     <row r="40" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C40" s="55"/>
       <c r="D40" s="74" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="E40" s="74"/>
       <c r="F40" s="1" t="s">
@@ -23352,7 +23361,7 @@
         <v>10</v>
       </c>
       <c r="J40" s="74" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="K40" s="74"/>
       <c r="L40" s="74"/>
@@ -23360,7 +23369,7 @@
     <row r="41" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C41" s="55"/>
       <c r="D41" s="74" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="E41" s="74"/>
       <c r="F41" s="1" t="s">
@@ -23374,7 +23383,7 @@
         <v>12</v>
       </c>
       <c r="J41" s="74" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="K41" s="74"/>
       <c r="L41" s="74"/>
@@ -23382,7 +23391,7 @@
     <row r="42" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C42" s="55"/>
       <c r="D42" s="74" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="E42" s="74"/>
       <c r="F42" s="1" t="s">
@@ -23400,7 +23409,7 @@
     <row r="43" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C43" s="55"/>
       <c r="D43" s="74" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="E43" s="74"/>
       <c r="F43" s="1" t="s">
@@ -23432,7 +23441,7 @@
         <v>20</v>
       </c>
       <c r="J44" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K44" s="74"/>
       <c r="L44" s="74"/>
@@ -23440,7 +23449,7 @@
     <row r="45" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C45" s="56"/>
       <c r="D45" s="74" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="E45" s="74"/>
       <c r="F45" s="1" t="s">
@@ -23452,7 +23461,7 @@
       <c r="H45" s="57"/>
       <c r="I45" s="1"/>
       <c r="J45" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K45" s="74"/>
       <c r="L45" s="74"/>
@@ -23474,7 +23483,7 @@
         <v>10</v>
       </c>
       <c r="J46" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K46" s="74"/>
       <c r="L46" s="74"/>
@@ -23482,7 +23491,7 @@
     <row r="47" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C47" s="56"/>
       <c r="D47" s="74" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="E47" s="74"/>
       <c r="F47" s="1" t="s">
@@ -23496,7 +23505,7 @@
         <v>9</v>
       </c>
       <c r="J47" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K47" s="74"/>
       <c r="L47" s="74"/>
@@ -23504,7 +23513,7 @@
     <row r="48" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C48" s="56"/>
       <c r="D48" s="74" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="E48" s="74"/>
       <c r="F48" s="1" t="s">
@@ -23540,11 +23549,11 @@
     <row r="50" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C50" s="56"/>
       <c r="D50" s="74" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E50" s="74"/>
       <c r="F50" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G50" s="1">
         <v>0</v>
@@ -23554,7 +23563,7 @@
         <v>8</v>
       </c>
       <c r="J50" s="74" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="K50" s="74"/>
       <c r="L50" s="74"/>
@@ -23562,11 +23571,11 @@
     <row r="51" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C51" s="56"/>
       <c r="D51" s="74" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="E51" s="74"/>
       <c r="F51" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G51" s="1">
         <v>0</v>
@@ -23576,7 +23585,7 @@
         <v>8</v>
       </c>
       <c r="J51" s="74" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="K51" s="74"/>
       <c r="L51" s="74"/>
@@ -23584,11 +23593,11 @@
     <row r="52" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C52" s="56"/>
       <c r="D52" s="74" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="E52" s="74"/>
       <c r="F52" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="G52" s="1">
         <v>0</v>
@@ -23598,7 +23607,7 @@
         <v>10</v>
       </c>
       <c r="J52" s="74" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="K52" s="74"/>
       <c r="L52" s="74"/>
@@ -23620,7 +23629,7 @@
         <v>20</v>
       </c>
       <c r="J53" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K53" s="74"/>
       <c r="L53" s="74"/>
@@ -23628,7 +23637,7 @@
     <row r="54" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C54" s="56"/>
       <c r="D54" s="74" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="E54" s="74"/>
       <c r="F54" s="1" t="s">
@@ -23642,7 +23651,7 @@
         <v>11</v>
       </c>
       <c r="J54" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K54" s="74"/>
       <c r="L54" s="74"/>
@@ -23650,7 +23659,7 @@
     <row r="55" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C55" s="56"/>
       <c r="D55" s="74" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="E55" s="74"/>
       <c r="F55" s="1" t="s">
@@ -23664,7 +23673,7 @@
         <v>29</v>
       </c>
       <c r="J55" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K55" s="74"/>
       <c r="L55" s="74"/>
@@ -23672,7 +23681,7 @@
     <row r="56" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C56" s="56"/>
       <c r="D56" s="74" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="E56" s="74"/>
       <c r="F56" s="1" t="s">
@@ -23686,7 +23695,7 @@
         <v>19</v>
       </c>
       <c r="J56" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K56" s="74"/>
       <c r="L56" s="74"/>
@@ -23694,7 +23703,7 @@
     <row r="57" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C57" s="56"/>
       <c r="D57" s="74" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="E57" s="74"/>
       <c r="F57" s="1" t="s">
@@ -23708,7 +23717,7 @@
         <v>13</v>
       </c>
       <c r="J57" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K57" s="74"/>
       <c r="L57" s="74"/>
@@ -23716,7 +23725,7 @@
     <row r="58" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C58" s="56"/>
       <c r="D58" s="74" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="E58" s="74"/>
       <c r="F58" s="1" t="s">
@@ -23730,7 +23739,7 @@
         <v>10</v>
       </c>
       <c r="J58" s="74" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="K58" s="74"/>
       <c r="L58" s="74"/>
@@ -23750,7 +23759,7 @@
       <c r="H59" s="57"/>
       <c r="I59" s="1"/>
       <c r="J59" s="74" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="K59" s="74"/>
       <c r="L59" s="74"/>
@@ -23758,7 +23767,7 @@
     <row r="60" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C60" s="56"/>
       <c r="D60" s="74" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="E60" s="74"/>
       <c r="F60" s="1" t="s">
@@ -23768,7 +23777,7 @@
       <c r="H60" s="57"/>
       <c r="I60" s="1"/>
       <c r="J60" s="74" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="K60" s="74"/>
       <c r="L60" s="74"/>
@@ -23776,7 +23785,7 @@
     <row r="61" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C61" s="56"/>
       <c r="D61" s="74" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E61" s="74"/>
       <c r="F61" s="1" t="s">
@@ -23788,7 +23797,7 @@
       <c r="H61" s="57"/>
       <c r="I61" s="1"/>
       <c r="J61" s="74" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="K61" s="74"/>
       <c r="L61" s="74"/>
@@ -23796,7 +23805,7 @@
     <row r="62" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C62" s="56"/>
       <c r="D62" s="74" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E62" s="74"/>
       <c r="F62" s="1" t="s">
@@ -23812,7 +23821,7 @@
     <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C63" s="56"/>
       <c r="D63" s="74" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E63" s="74"/>
       <c r="F63" s="1" t="s">
@@ -23830,7 +23839,7 @@
     <row r="64" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C64" s="56"/>
       <c r="D64" s="74" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="E64" s="74"/>
       <c r="F64" s="1" t="s">
@@ -23848,7 +23857,7 @@
     <row r="65" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C65" s="56"/>
       <c r="D65" s="74" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="E65" s="74"/>
       <c r="F65" s="1" t="s">
@@ -23866,7 +23875,7 @@
     <row r="66" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C66" s="56"/>
       <c r="D66" s="74" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="E66" s="74"/>
       <c r="F66" s="1" t="s">
@@ -23884,7 +23893,7 @@
     <row r="67" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C67" s="56"/>
       <c r="D67" s="74" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="E67" s="74"/>
       <c r="F67" s="1" t="s">
@@ -23898,7 +23907,7 @@
         <v>15</v>
       </c>
       <c r="J67" s="74" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K67" s="74"/>
       <c r="L67" s="74"/>
@@ -23906,7 +23915,7 @@
     <row r="68" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C68" s="56"/>
       <c r="D68" s="74" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="E68" s="74"/>
       <c r="F68" s="1" t="s">
@@ -23924,11 +23933,11 @@
     <row r="69" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C69" s="56"/>
       <c r="D69" s="74" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="E69" s="74"/>
       <c r="F69" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
@@ -23938,7 +23947,7 @@
         <v>30</v>
       </c>
       <c r="J69" s="74" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K69" s="74"/>
       <c r="L69" s="74"/>
@@ -23946,7 +23955,7 @@
     <row r="70" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C70" s="56"/>
       <c r="D70" s="74" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="E70" s="74"/>
       <c r="F70" s="1" t="s">
@@ -23960,7 +23969,7 @@
         <v>20</v>
       </c>
       <c r="J70" s="74" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K70" s="74"/>
       <c r="L70" s="74"/>
@@ -23968,7 +23977,7 @@
     <row r="71" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C71" s="56"/>
       <c r="D71" s="74" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="E71" s="74"/>
       <c r="F71" s="1" t="s">
@@ -23982,7 +23991,7 @@
         <v>16</v>
       </c>
       <c r="J71" s="74" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="K71" s="74"/>
       <c r="L71" s="74"/>
@@ -23990,7 +23999,7 @@
     <row r="72" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C72" s="56"/>
       <c r="D72" s="74" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="E72" s="74"/>
       <c r="F72" s="1" t="s">
@@ -24008,7 +24017,7 @@
     <row r="73" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C73" s="56"/>
       <c r="D73" s="74" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="E73" s="74"/>
       <c r="F73" s="1" t="s">
@@ -24074,7 +24083,7 @@
       <c r="H76" s="57"/>
       <c r="I76" s="1"/>
       <c r="J76" s="74" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="K76" s="74"/>
       <c r="L76" s="74"/>
@@ -24082,7 +24091,7 @@
     <row r="77" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C77" s="56"/>
       <c r="D77" s="152" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="E77" s="153"/>
       <c r="F77" s="32" t="s">
@@ -24118,7 +24127,7 @@
     <row r="79" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C79" s="56"/>
       <c r="D79" s="74" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E79" s="74"/>
       <c r="F79" s="1" t="s">
@@ -24148,7 +24157,7 @@
       <c r="H80" s="57"/>
       <c r="I80" s="1"/>
       <c r="J80" s="74" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="K80" s="74"/>
       <c r="L80" s="74"/>
@@ -24156,7 +24165,7 @@
     <row r="81" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C81" s="56"/>
       <c r="D81" s="74" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="E81" s="74"/>
       <c r="F81" s="1" t="s">
@@ -24174,7 +24183,7 @@
     <row r="82" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C82" s="56"/>
       <c r="D82" s="74" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="E82" s="74"/>
       <c r="F82" s="1" t="s">
@@ -24192,7 +24201,7 @@
     <row r="83" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C83" s="56"/>
       <c r="D83" s="74" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="E83" s="74"/>
       <c r="F83" s="1" t="s">
@@ -24210,7 +24219,7 @@
     <row r="84" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C84" s="56"/>
       <c r="D84" s="74" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="E84" s="74"/>
       <c r="F84" s="1" t="s">
@@ -24315,8 +24324,8 @@
     </row>
     <row r="91" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C91" s="55"/>
-      <c r="D91" s="79"/>
-      <c r="E91" s="80"/>
+      <c r="D91" s="82"/>
+      <c r="E91" s="83"/>
       <c r="F91" s="1"/>
       <c r="G91" s="1"/>
       <c r="H91" s="1"/>
@@ -24339,8 +24348,8 @@
     </row>
     <row r="93" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C93" s="1"/>
-      <c r="D93" s="79"/>
-      <c r="E93" s="80"/>
+      <c r="D93" s="82"/>
+      <c r="E93" s="83"/>
       <c r="F93" s="3"/>
       <c r="G93" s="4"/>
       <c r="H93" s="4"/>
@@ -24351,8 +24360,8 @@
     </row>
     <row r="94" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C94" s="1"/>
-      <c r="D94" s="79"/>
-      <c r="E94" s="80"/>
+      <c r="D94" s="82"/>
+      <c r="E94" s="83"/>
       <c r="F94" s="14"/>
       <c r="G94" s="4">
         <f>SUM(G20:G92)</f>
@@ -24395,18 +24404,18 @@
       <c r="L96" s="90"/>
     </row>
     <row r="97" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C97" s="81" t="s">
+      <c r="C97" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D97" s="82"/>
-      <c r="E97" s="82"/>
-      <c r="F97" s="82"/>
-      <c r="G97" s="82"/>
-      <c r="H97" s="82"/>
-      <c r="I97" s="82"/>
-      <c r="J97" s="82"/>
-      <c r="K97" s="82"/>
-      <c r="L97" s="83"/>
+      <c r="D97" s="76"/>
+      <c r="E97" s="76"/>
+      <c r="F97" s="76"/>
+      <c r="G97" s="76"/>
+      <c r="H97" s="76"/>
+      <c r="I97" s="76"/>
+      <c r="J97" s="76"/>
+      <c r="K97" s="76"/>
+      <c r="L97" s="77"/>
     </row>
     <row r="98" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C98" s="6" t="s">
@@ -24442,7 +24451,7 @@
         <v>523</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="F99" s="1" t="s">
         <v>219</v>
@@ -24459,13 +24468,13 @@
     <row r="100" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C100" s="27"/>
       <c r="D100" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="E100" s="1" t="s">
         <v>707</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="F100" s="1" t="s">
         <v>708</v>
-      </c>
-      <c r="F100" s="1" t="s">
-        <v>709</v>
       </c>
       <c r="G100" s="1">
         <v>4.5999999999999996</v>
@@ -24479,13 +24488,13 @@
     <row r="101" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C101" s="27"/>
       <c r="D101" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="F101" s="1" t="s">
         <v>708</v>
-      </c>
-      <c r="E101" s="1" t="s">
-        <v>710</v>
-      </c>
-      <c r="F101" s="1" t="s">
-        <v>709</v>
       </c>
       <c r="G101" s="1">
         <v>4.5999999999999996</v>
@@ -24499,13 +24508,13 @@
     <row r="102" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C102" s="27"/>
       <c r="D102" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="G102" s="1"/>
       <c r="H102" s="1"/>
@@ -24517,7 +24526,7 @@
     <row r="103" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C103" s="27"/>
       <c r="D103" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>523</v>
@@ -24634,7 +24643,7 @@
         <v>541</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F109" s="1"/>
       <c r="G109" s="1"/>
@@ -24647,7 +24656,7 @@
     <row r="110" spans="3:12" x14ac:dyDescent="0.2">
       <c r="C110" s="27"/>
       <c r="D110" s="1" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>519</v>
@@ -24786,9 +24795,9 @@
         <v>0</v>
       </c>
       <c r="I119" s="3"/>
-      <c r="J119" s="75"/>
-      <c r="K119" s="75"/>
-      <c r="L119" s="75"/>
+      <c r="J119" s="78"/>
+      <c r="K119" s="78"/>
+      <c r="L119" s="78"/>
     </row>
     <row r="120" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D120" s="38"/>
@@ -24958,12 +24967,8 @@
     <mergeCell ref="J33:L33"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="J30:L30"/>
-    <mergeCell ref="N24:R24"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="J31:L31"/>
-    <mergeCell ref="Q25:R25"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="J27:L27"/>
     <mergeCell ref="N31:R31"/>
     <mergeCell ref="D28:E28"/>
     <mergeCell ref="J28:L28"/>
@@ -24971,18 +24976,18 @@
     <mergeCell ref="J29:L29"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="J25:L25"/>
-    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q27:R27"/>
     <mergeCell ref="D26:E26"/>
     <mergeCell ref="J26:L26"/>
-    <mergeCell ref="Q20:R20"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="J23:L23"/>
     <mergeCell ref="Q26:R26"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="J24:L24"/>
-    <mergeCell ref="Q27:R27"/>
     <mergeCell ref="D21:E21"/>
     <mergeCell ref="J21:L21"/>
+    <mergeCell ref="N24:R24"/>
+    <mergeCell ref="Q25:R25"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="J27:L27"/>
     <mergeCell ref="Q15:R15"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="J22:L22"/>
@@ -25002,6 +25007,10 @@
     <mergeCell ref="C18:L18"/>
     <mergeCell ref="Q17:R17"/>
     <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="Q20:R20"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="J23:L23"/>
     <mergeCell ref="N12:R12"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="N2:P2"/>
@@ -25058,11 +25067,11 @@
       <c r="J2" s="97"/>
       <c r="K2" s="97"/>
       <c r="L2" s="97"/>
-      <c r="N2" s="81" t="s">
+      <c r="N2" s="75" t="s">
         <v>44</v>
       </c>
-      <c r="O2" s="82"/>
-      <c r="P2" s="83"/>
+      <c r="O2" s="76"/>
+      <c r="P2" s="77"/>
       <c r="R2" s="34" t="s">
         <v>338</v>
       </c>
@@ -25301,13 +25310,13 @@
       <c r="J12" s="96"/>
       <c r="K12" s="96"/>
       <c r="L12" s="96"/>
-      <c r="N12" s="81" t="s">
+      <c r="N12" s="75" t="s">
         <v>69</v>
       </c>
-      <c r="O12" s="82"/>
-      <c r="P12" s="82"/>
-      <c r="Q12" s="82"/>
-      <c r="R12" s="83"/>
+      <c r="O12" s="76"/>
+      <c r="P12" s="76"/>
+      <c r="Q12" s="76"/>
+      <c r="R12" s="77"/>
     </row>
     <row r="13" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C13" s="12" t="s">
@@ -25327,13 +25336,13 @@
         <v>53</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="J13" s="88" t="s">
         <v>7</v>
       </c>
       <c r="K13" s="88"/>
-      <c r="L13" s="78"/>
+      <c r="L13" s="81"/>
       <c r="N13" s="6" t="s">
         <v>45</v>
       </c>
@@ -25343,10 +25352,10 @@
       <c r="P13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="Q13" s="77" t="s">
+      <c r="Q13" s="80" t="s">
         <v>7</v>
       </c>
-      <c r="R13" s="78"/>
+      <c r="R13" s="81"/>
     </row>
     <row r="14" spans="2:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C14" s="55"/>
@@ -25635,13 +25644,13 @@
       <c r="J24" s="74"/>
       <c r="K24" s="74"/>
       <c r="L24" s="74"/>
-      <c r="N24" s="81" t="s">
+      <c r="N24" s="75" t="s">
         <v>38</v>
       </c>
-      <c r="O24" s="82"/>
-      <c r="P24" s="82"/>
-      <c r="Q24" s="82"/>
-      <c r="R24" s="82"/>
+      <c r="O24" s="76"/>
+      <c r="P24" s="76"/>
+      <c r="Q24" s="76"/>
+      <c r="R24" s="76"/>
     </row>
     <row r="25" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C25" s="56"/>
@@ -25667,7 +25676,7 @@
       <c r="P25" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="Q25" s="77" t="s">
+      <c r="Q25" s="80" t="s">
         <v>7</v>
       </c>
       <c r="R25" s="88"/>
@@ -25817,13 +25826,13 @@
       </c>
       <c r="K31" s="74"/>
       <c r="L31" s="74"/>
-      <c r="N31" s="81" t="s">
+      <c r="N31" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="O31" s="82"/>
-      <c r="P31" s="82"/>
-      <c r="Q31" s="82"/>
-      <c r="R31" s="83"/>
+      <c r="O31" s="76"/>
+      <c r="P31" s="76"/>
+      <c r="Q31" s="76"/>
+      <c r="R31" s="77"/>
     </row>
     <row r="32" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C32" s="55"/>
@@ -25951,12 +25960,12 @@
       </c>
       <c r="K36" s="74"/>
       <c r="L36" s="74"/>
-      <c r="N36" s="81" t="s">
+      <c r="N36" s="75" t="s">
         <v>57</v>
       </c>
-      <c r="O36" s="82"/>
-      <c r="P36" s="82"/>
-      <c r="Q36" s="83"/>
+      <c r="O36" s="76"/>
+      <c r="P36" s="76"/>
+      <c r="Q36" s="77"/>
     </row>
     <row r="37" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C37" s="55"/>
@@ -26100,8 +26109,8 @@
     </row>
     <row r="43" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C43" s="56"/>
-      <c r="D43" s="79"/>
-      <c r="E43" s="80"/>
+      <c r="D43" s="82"/>
+      <c r="E43" s="83"/>
       <c r="F43" s="1"/>
       <c r="G43" s="1"/>
       <c r="H43" s="57"/>
@@ -26112,8 +26121,8 @@
     </row>
     <row r="44" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C44" s="55"/>
-      <c r="D44" s="79"/>
-      <c r="E44" s="80"/>
+      <c r="D44" s="82"/>
+      <c r="E44" s="83"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
@@ -26136,8 +26145,8 @@
     </row>
     <row r="46" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C46" s="1"/>
-      <c r="D46" s="79"/>
-      <c r="E46" s="80"/>
+      <c r="D46" s="82"/>
+      <c r="E46" s="83"/>
       <c r="F46" s="3"/>
       <c r="G46" s="4"/>
       <c r="H46" s="4"/>
@@ -26148,8 +26157,8 @@
     </row>
     <row r="47" spans="3:18" ht="19" x14ac:dyDescent="0.25">
       <c r="C47" s="1"/>
-      <c r="D47" s="79"/>
-      <c r="E47" s="80"/>
+      <c r="D47" s="82"/>
+      <c r="E47" s="83"/>
       <c r="F47" s="14"/>
       <c r="G47" s="4">
         <f>SUM(G14:G45)</f>
@@ -26192,18 +26201,18 @@
       <c r="L49" s="90"/>
     </row>
     <row r="50" spans="3:12" ht="19" x14ac:dyDescent="0.25">
-      <c r="C50" s="81" t="s">
+      <c r="C50" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="D50" s="82"/>
-      <c r="E50" s="82"/>
-      <c r="F50" s="82"/>
-      <c r="G50" s="82"/>
-      <c r="H50" s="82"/>
-      <c r="I50" s="82"/>
-      <c r="J50" s="82"/>
-      <c r="K50" s="82"/>
-      <c r="L50" s="83"/>
+      <c r="D50" s="76"/>
+      <c r="E50" s="76"/>
+      <c r="F50" s="76"/>
+      <c r="G50" s="76"/>
+      <c r="H50" s="76"/>
+      <c r="I50" s="76"/>
+      <c r="J50" s="76"/>
+      <c r="K50" s="76"/>
+      <c r="L50" s="77"/>
     </row>
     <row r="51" spans="3:12" ht="19" x14ac:dyDescent="0.25">
       <c r="C51" s="6" t="s">
@@ -26409,9 +26418,9 @@
         <v>0</v>
       </c>
       <c r="I62" s="3"/>
-      <c r="J62" s="75"/>
-      <c r="K62" s="75"/>
-      <c r="L62" s="75"/>
+      <c r="J62" s="78"/>
+      <c r="K62" s="78"/>
+      <c r="L62" s="78"/>
     </row>
     <row r="63" spans="3:12" x14ac:dyDescent="0.2">
       <c r="D63" s="38"/>
@@ -26483,11 +26492,7 @@
     <mergeCell ref="J36:L36"/>
     <mergeCell ref="N29:R30"/>
     <mergeCell ref="N31:R31"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="J21:L21"/>
     <mergeCell ref="Q27:R27"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="J22:L22"/>
     <mergeCell ref="Q28:R28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="J29:L29"/>
@@ -26495,23 +26500,22 @@
     <mergeCell ref="J30:L30"/>
     <mergeCell ref="Q25:R25"/>
     <mergeCell ref="Q26:R26"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="N22:R23"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="J17:L17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="J25:L25"/>
     <mergeCell ref="N24:R24"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="J23:L23"/>
     <mergeCell ref="Q20:R20"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="J24:L24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="J25:L25"/>
     <mergeCell ref="Q21:R21"/>
-    <mergeCell ref="C10:L11"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="J21:L21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="J22:L22"/>
+    <mergeCell ref="N22:R23"/>
     <mergeCell ref="Q16:R16"/>
     <mergeCell ref="Q17:R17"/>
     <mergeCell ref="C12:L12"/>
@@ -26523,8 +26527,12 @@
     <mergeCell ref="Q13:R13"/>
     <mergeCell ref="D19:E19"/>
     <mergeCell ref="J19:L19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="J20:L20"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="J18:L18"/>
     <mergeCell ref="I8:K8"/>
     <mergeCell ref="Q14:R14"/>
     <mergeCell ref="I9:K9"/>
@@ -26540,6 +26548,7 @@
     <mergeCell ref="J14:L14"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="J15:L15"/>
+    <mergeCell ref="C10:L11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
